--- a/docs/templates/employees-shablon.xlsx
+++ b/docs/templates/employees-shablon.xlsx
@@ -8,6 +8,23 @@
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="G2" authorId="0">
+      <text>
+        <r>
+          <t>avval /departments orqali yaratiladi</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,5 +544,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/templates/employees-shablon.xlsx
+++ b/docs/templates/employees-shablon.xlsx
@@ -5,6 +5,7 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Import" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Yo'riqnoma" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -19,7 +20,7 @@
     <comment ref="G2" authorId="0">
       <text>
         <r>
-          <t>avval /departments orqali yaratiladi</t>
+          <t>Bu bo'lim avval tizimda yaratilgan bo'lishi kerak (Ma'lumotnomalar → Bo'limlar)</t>
         </r>
       </text>
     </comment>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="40">
   <si>
     <t>xodim_kodi</t>
   </si>
@@ -85,6 +86,69 @@
   </si>
   <si>
     <t>SALES_REP</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>ustun</t>
+  </si>
+  <si>
+    <t>majburiymi</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>misol</t>
+  </si>
+  <si>
+    <t>Ha</t>
+  </si>
+  <si>
+    <t>Matn, ko'pi bilan 50 belgi. Xodim faqat shu kod bilan aniqlanadi</t>
+  </si>
+  <si>
+    <t>Yo'q</t>
+  </si>
+  <si>
+    <t>Matn, ko'pi bilan 100 belgi</t>
+  </si>
+  <si>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun</t>
+  </si>
+  <si>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun. Ishdan ketmagan bo'lsa — bo'sh qoldiring</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>Lavozim berilsa — ha</t>
+  </si>
+  <si>
+    <t>Bo'lim kodi (Ma'lumotnomalar → Bo'limlar). bolim_kodi, lavozim_kodi va lavozim_sanasi birga to'ldiriladi</t>
+  </si>
+  <si>
+    <t>Lavozim kodi: SALES_REP, SUPERVISOR, OPERATOR yoki EXPEDITOR</t>
+  </si>
+  <si>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; faqat oyning 1-kuni (masalan 2025-02-01)</t>
+  </si>
+  <si>
+    <t>Oylik berilsa — ha</t>
+  </si>
+  <si>
+    <t>Son, so'mda; kasr ko'pi bilan 2 belgi. Minglik bo'shliq mumkin (3 000 000)</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>2-qatordagi namuna — faqat ko'rsatma. Uni o'chirib, o'z ma'lumotingizni yozing, aks holda namuna ham import qilinadi.</t>
+  </si>
+  <si>
+    <t>1-qator (sarlavha) o'zgarmasligi kerak. Import faqat shu faylning birinchi varag'ini o'qiydi — «Yo'riqnoma» varag'i hisobga olinmaydi.</t>
   </si>
 </sst>
 </file>
@@ -123,9 +187,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,7 +538,17 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="20" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -532,13 +612,13 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>3000000</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -546,4 +626,199 @@
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/templates/employees-shablon.xlsx
+++ b/docs/templates/employees-shablon.xlsx
@@ -17,7 +17,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <t>Bu bo'lim avval tizimda yaratilgan bo'lishi kerak (Ma'lumotnomalar → Bo'limlar)</t>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>xodim_kodi</t>
   </si>
@@ -64,9 +64,33 @@
     <t>oylik_sanasi</t>
   </si>
   <si>
+    <t>ustun</t>
+  </si>
+  <si>
+    <t>majburiymi</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>misol</t>
+  </si>
+  <si>
+    <t>Ha</t>
+  </si>
+  <si>
+    <t>Matn, ko'pi bilan 50 belgi. Xodim faqat shu kod bilan aniqlanadi</t>
+  </si>
+  <si>
     <t>E001</t>
   </si>
   <si>
+    <t>Yo'q</t>
+  </si>
+  <si>
+    <t>Matn, ko'pi bilan 100 belgi</t>
+  </si>
+  <si>
     <t>Aliyev</t>
   </si>
   <si>
@@ -76,64 +100,37 @@
     <t>Karimovich</t>
   </si>
   <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t/>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun. Ishdan ketmagan bo'lsa — bo'sh qoldiring</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>Lavozim berilsa — ha</t>
+  </si>
+  <si>
+    <t>Bo'lim kodi (Ma'lumotnomalar → Bo'limlar). bolim_kodi, lavozim_kodi va lavozim_sanasi birga to'ldiriladi</t>
   </si>
   <si>
     <t>SAVDO</t>
   </si>
   <si>
+    <t>Lavozim kodi: SALES_REP, SUPERVISOR, OPERATOR yoki EXPEDITOR</t>
+  </si>
+  <si>
     <t>SALES_REP</t>
   </si>
   <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>ustun</t>
-  </si>
-  <si>
-    <t>majburiymi</t>
-  </si>
-  <si>
-    <t>format</t>
-  </si>
-  <si>
-    <t>misol</t>
-  </si>
-  <si>
-    <t>Ha</t>
-  </si>
-  <si>
-    <t>Matn, ko'pi bilan 50 belgi. Xodim faqat shu kod bilan aniqlanadi</t>
-  </si>
-  <si>
-    <t>Yo'q</t>
-  </si>
-  <si>
-    <t>Matn, ko'pi bilan 100 belgi</t>
-  </si>
-  <si>
-    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun</t>
-  </si>
-  <si>
-    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; istalgan kun. Ishdan ketmagan bo'lsa — bo'sh qoldiring</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>Lavozim berilsa — ha</t>
-  </si>
-  <si>
-    <t>Bo'lim kodi (Ma'lumotnomalar → Bo'limlar). bolim_kodi, lavozim_kodi va lavozim_sanasi birga to'ldiriladi</t>
-  </si>
-  <si>
-    <t>Lavozim kodi: SALES_REP, SUPERVISOR, OPERATOR yoki EXPEDITOR</t>
-  </si>
-  <si>
-    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; faqat oyning 1-kuni (masalan 2025-02-01)</t>
+    <t>Sana: YYYY-MM-DD yoki DD.MM.YYYY; faqat oyning 1-kuni (masalan 2026-02-01)</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
   </si>
   <si>
     <t>Oylik berilsa — ha</t>
@@ -145,7 +142,7 @@
     <t>3000000</t>
   </si>
   <si>
-    <t>2-qatordagi namuna — faqat ko'rsatma. Uni o'chirib, o'z ma'lumotingizni yozing, aks holda namuna ham import qilinadi.</t>
+    <t>«misol» ustunidagi qiymatlar — faqat ko'rsatma. 1-varaqning 2-qatoridan boshlab o'z ma'lumotingizni yozing.</t>
   </si>
   <si>
     <t>1-qator (sarlavha) o'zgarmasligi kerak. Import faqat shu faylning birinchi varag'ini o'qiydi — «Yo'riqnoma» varag'i hisobga olinmaydi.</t>
@@ -535,19 +532,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -584,41 +581,6 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>3000000</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -641,16 +603,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,13 +620,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,13 +634,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,13 +648,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -700,13 +662,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,13 +676,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,13 +690,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,13 +704,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,13 +718,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -770,13 +732,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -784,13 +746,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -798,23 +760,23 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
